--- a/region/Central-overview-grid.xlsx
+++ b/region/Central-overview-grid.xlsx
@@ -112,7 +112,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AD28"/>
+  <dimension ref="A1:AD29"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="14" customWidth="1"/>
@@ -150,7 +150,7 @@
     <row r="1" ht="20" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">H-E-B  |  Region Overview information — Central — generated 8/5/2026</t>
+          <t xml:space="preserve">H-E-B  |  Region Overview information — Central — generated 8/11/2026</t>
         </is>
       </c>
     </row>
@@ -584,7 +584,7 @@
       <c r="P6" s="4"/>
       <c r="Q6" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Big Outdoor QD01 — ATX.SP104 Palm Way wallscape (The Domain, Austin) — HEB-SIGNED 8/4/26, awaiting BIG officer acceptance (Unique OOH — never enters billboard master)</t>
+          <t xml:space="preserve">Big Outdoor QD01 — ATX.SP104 Palm Way wallscape (The Domain, Austin), 10/19/26–1/3/27 — ✅ EXECUTED 8/7/26 (Sowrey 8/4 + Rappaport 8/7)</t>
         </is>
       </c>
       <c r="R6" s="6">
@@ -595,7 +595,7 @@
       </c>
       <c r="T6" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Big Outdoor QD01 ATX.SP104 HEB-SIGNED 8-4-26 (awaiting BIG officer acceptance).pdf</t>
+          <t xml:space="preserve">Big Outdoor QD01 ATX.SP104 EXECUTED 8-7-26 (both signed).pdf</t>
         </is>
       </c>
       <c r="U6" s="4">
@@ -2892,22 +2892,18 @@
     <row r="28">
       <c r="A28" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">203-8051L</t>
+          <t xml:space="preserve">189-3</t>
         </is>
       </c>
       <c r="B28" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Theon Properties</t>
-        </is>
-      </c>
-      <c r="C28" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Mike Elliott (Elliott Properties Inc)</t>
-        </is>
-      </c>
+          <t xml:space="preserve">The Reiss Group</t>
+        </is>
+      </c>
+      <c r="C28" s="4"/>
       <c r="D28" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">mike@elliottpropertiesinc.com</t>
+          <t xml:space="preserve">Lisa@thereissgroup.net</t>
         </is>
       </c>
       <c r="E28" s="4" t="inlineStr">
@@ -2923,77 +2919,175 @@
       <c r="G28" s="4"/>
       <c r="H28" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">IH-35 NB, 0.5 mi south of Ronald Reagan Blvd — SW corner IH-35 &amp; Ronald Reagan ("Sign No. 2"), 8360 I-35 frontage, Georgetown/Jarrell line</t>
-        </is>
-      </c>
-      <c r="I28" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Jarrell</t>
-        </is>
-      </c>
-      <c r="J28" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">78626</t>
-        </is>
-      </c>
+          <t xml:space="preserve">I-35 near Hwy 123 (MP 203.7), 408 Patricia Dr, San Marcos, TX</t>
+        </is>
+      </c>
+      <c r="I28" s="4"/>
+      <c r="J28" s="4"/>
       <c r="K28" s="10">
-        <v>30.7645</v>
+        <v>29.86349</v>
       </c>
       <c r="L28" s="10">
-        <v>-97.6302</v>
-      </c>
-      <c r="M28" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">South</t>
-        </is>
-      </c>
-      <c r="N28" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Left</t>
-        </is>
-      </c>
+        <v>-97.94506</v>
+      </c>
+      <c r="M28" s="4"/>
+      <c r="N28" s="4"/>
       <c r="O28" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">14x48</t>
-        </is>
-      </c>
-      <c r="P28" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Y</t>
-        </is>
-      </c>
-      <c r="Q28" s="4"/>
+          <t xml:space="preserve">12'' x 40''</t>
+        </is>
+      </c>
+      <c r="P28" s="4"/>
+      <c r="Q28" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">SM3 GO</t>
+        </is>
+      </c>
       <c r="R28" s="6">
-        <v>46296</v>
+        <v>46237</v>
       </c>
       <c r="S28" s="6">
-        <v>47026</v>
+        <v>46355</v>
       </c>
       <c r="T28" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Theon 8051L lease EXECUTED 8-4-26 (both signed).pdf</t>
+          <t xml:space="preserve">Sam Marcos_GD.pdf</t>
         </is>
       </c>
       <c r="U28" s="4">
-        <v>256803</v>
+        <v>367525</v>
       </c>
       <c r="V28" s="8">
-        <v>1000</v>
+        <v>3090</v>
       </c>
       <c r="W28" s="8"/>
       <c r="X28" s="4"/>
       <c r="Y28" s="4">
-        <v>8.4</v>
+        <v>0.9</v>
       </c>
       <c r="Z28" s="12" t="inlineStr">
         <is>
           <t xml:space="preserve">📐 Spec Sheet</t>
         </is>
       </c>
-      <c r="AA28" s="4"/>
+      <c r="AA28" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">GO: Coming Soon</t>
+        </is>
+      </c>
       <c r="AB28" s="4"/>
       <c r="AC28" s="6"/>
-      <c r="AD28" s="4"/>
+      <c r="AD28" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">GO: Date Reveal</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">203-8051L</t>
+        </is>
+      </c>
+      <c r="B29" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Theon Properties</t>
+        </is>
+      </c>
+      <c r="C29" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Mike Elliott (Elliott Properties Inc)</t>
+        </is>
+      </c>
+      <c r="D29" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">mike@elliottpropertiesinc.com</t>
+        </is>
+      </c>
+      <c r="E29" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Central</t>
+        </is>
+      </c>
+      <c r="F29" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Bulletin</t>
+        </is>
+      </c>
+      <c r="G29" s="5"/>
+      <c r="H29" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">IH-35 NB, 0.5 mi south of Ronald Reagan Blvd — SW corner IH-35 &amp; Ronald Reagan ("Sign No. 2"), 8360 I-35 frontage, Georgetown/Jarrell line</t>
+        </is>
+      </c>
+      <c r="I29" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Jarrell</t>
+        </is>
+      </c>
+      <c r="J29" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">78626</t>
+        </is>
+      </c>
+      <c r="K29" s="11">
+        <v>30.7645</v>
+      </c>
+      <c r="L29" s="11">
+        <v>-97.6302</v>
+      </c>
+      <c r="M29" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">South</t>
+        </is>
+      </c>
+      <c r="N29" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Left</t>
+        </is>
+      </c>
+      <c r="O29" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">14x48</t>
+        </is>
+      </c>
+      <c r="P29" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Y</t>
+        </is>
+      </c>
+      <c r="Q29" s="5"/>
+      <c r="R29" s="7">
+        <v>46296</v>
+      </c>
+      <c r="S29" s="7">
+        <v>47026</v>
+      </c>
+      <c r="T29" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Theon 8051L lease EXECUTED 8-4-26 (both signed).pdf</t>
+        </is>
+      </c>
+      <c r="U29" s="5">
+        <v>256803</v>
+      </c>
+      <c r="V29" s="9">
+        <v>1000</v>
+      </c>
+      <c r="W29" s="9"/>
+      <c r="X29" s="5"/>
+      <c r="Y29" s="5">
+        <v>8.4</v>
+      </c>
+      <c r="Z29" s="13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">📐 Spec Sheet</t>
+        </is>
+      </c>
+      <c r="AA29" s="5"/>
+      <c r="AB29" s="5"/>
+      <c r="AC29" s="7"/>
+      <c r="AD29" s="5"/>
     </row>
   </sheetData>
   <autoFilter ref="A3:AD3"/>
@@ -3025,6 +3119,7 @@
     <hyperlink ref="Z26" r:id="rIdH21"/>
     <hyperlink ref="Z27" r:id="rIdH22"/>
     <hyperlink ref="Z28" r:id="rIdH23"/>
+    <hyperlink ref="Z29" r:id="rIdH24"/>
   </hyperlinks>
 </worksheet>
 </file>
--- a/region/Central-overview-grid.xlsx
+++ b/region/Central-overview-grid.xlsx
@@ -112,7 +112,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AD29"/>
+  <dimension ref="A1:AD30"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="14" customWidth="1"/>
@@ -1800,7 +1800,7 @@
     <row r="18">
       <c r="A18" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">TX90B</t>
+          <t xml:space="preserve">TX114A</t>
         </is>
       </c>
       <c r="B18" s="4" t="inlineStr">
@@ -1831,28 +1831,28 @@
       <c r="G18" s="4"/>
       <c r="H18" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">E/S of FM 1325, 550 ft E/o CR 172, N/F</t>
+          <t xml:space="preserve">E/S of IH-35, 250 feet S/o Old Bastrop Road.    San Marcos, TX, S/F</t>
         </is>
       </c>
       <c r="I18" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Austin</t>
+          <t xml:space="preserve">New Braunfels</t>
         </is>
       </c>
       <c r="J18" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">78728</t>
+          <t xml:space="preserve">78130</t>
         </is>
       </c>
       <c r="K18" s="10">
-        <v>30.47405</v>
+        <v>29.7814682</v>
       </c>
       <c r="L18" s="10">
-        <v>-97.688408</v>
+        <v>-98.0324503</v>
       </c>
       <c r="M18" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">North</t>
+          <t xml:space="preserve">South</t>
         </is>
       </c>
       <c r="N18" s="4" t="inlineStr">
@@ -1862,7 +1862,7 @@
       </c>
       <c r="O18" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">12' x 40'</t>
+          <t xml:space="preserve">14' x 48'</t>
         </is>
       </c>
       <c r="P18" s="4" t="inlineStr">
@@ -1872,26 +1872,26 @@
       </c>
       <c r="Q18" s="4"/>
       <c r="R18" s="6">
-        <v>46251</v>
+        <v>46237</v>
       </c>
       <c r="S18" s="6">
-        <v>46327</v>
+        <v>46355</v>
       </c>
       <c r="T18" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">MH Outdoor 15447 TX90B HEB-SIGNED 8-4-26 (awaiting MH signature).pdf</t>
+          <t xml:space="preserve">Adkom_Contract_for_Signature_-_HEB.pdf</t>
         </is>
       </c>
       <c r="U18" s="4">
-        <v>353822</v>
+        <v>1931923</v>
       </c>
       <c r="V18" s="8">
-        <v>700</v>
+        <v>2818.66</v>
       </c>
       <c r="W18" s="8"/>
       <c r="X18" s="4"/>
       <c r="Y18" s="4">
-        <v>1.8</v>
+        <v>7.3</v>
       </c>
       <c r="Z18" s="12" t="inlineStr">
         <is>
@@ -1906,22 +1906,22 @@
     <row r="19">
       <c r="A19" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">134</t>
+          <t xml:space="preserve">TX90B</t>
         </is>
       </c>
       <c r="B19" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Reagan Outdoor</t>
+          <t xml:space="preserve">MH Outdoor Media</t>
         </is>
       </c>
       <c r="C19" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Karen Goumakos</t>
+          <t xml:space="preserve">Brandon Wilburn</t>
         </is>
       </c>
       <c r="D19" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">kgoumakos@reaganusa.com</t>
+          <t xml:space="preserve">bwilburn@machaik.com</t>
         </is>
       </c>
       <c r="E19" s="5" t="inlineStr">
@@ -1934,14 +1934,10 @@
           <t xml:space="preserve">Static Bulletin</t>
         </is>
       </c>
-      <c r="G19" s="5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">470717</t>
-        </is>
-      </c>
+      <c r="G19" s="5"/>
       <c r="H19" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">10720 I-35 N 0.3 mi S/O Braker Ln E WS</t>
+          <t xml:space="preserve">E/S of FM 1325, 550 ft E/o CR 172, N/F</t>
         </is>
       </c>
       <c r="I19" s="5" t="inlineStr">
@@ -1951,14 +1947,14 @@
       </c>
       <c r="J19" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">78753</t>
+          <t xml:space="preserve">78728</t>
         </is>
       </c>
       <c r="K19" s="11">
-        <v>30.373336</v>
+        <v>30.47405</v>
       </c>
       <c r="L19" s="11">
-        <v>-97.679089</v>
+        <v>-97.688408</v>
       </c>
       <c r="M19" s="5" t="inlineStr">
         <is>
@@ -1967,12 +1963,12 @@
       </c>
       <c r="N19" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Right</t>
+          <t xml:space="preserve">Left</t>
         </is>
       </c>
       <c r="O19" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">10' x 40'</t>
+          <t xml:space="preserve">12' x 40'</t>
         </is>
       </c>
       <c r="P19" s="5" t="inlineStr">
@@ -1985,23 +1981,23 @@
         <v>46251</v>
       </c>
       <c r="S19" s="7">
-        <v>46383</v>
+        <v>46327</v>
       </c>
       <c r="T19" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Reagan Q3Q4 2026 Bulletin HEB-signed (awaiting RNA President).pdf</t>
+          <t xml:space="preserve">MH Outdoor 15447 TX90B HEB-SIGNED 8-4-26 (awaiting MH signature).pdf</t>
         </is>
       </c>
       <c r="U19" s="5">
-        <v>727696</v>
+        <v>353822</v>
       </c>
       <c r="V19" s="9">
-        <v>6350</v>
+        <v>700</v>
       </c>
       <c r="W19" s="9"/>
       <c r="X19" s="5"/>
       <c r="Y19" s="5">
-        <v>1.3</v>
+        <v>1.8</v>
       </c>
       <c r="Z19" s="13" t="inlineStr">
         <is>
@@ -2016,7 +2012,7 @@
     <row r="20">
       <c r="A20" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">352</t>
+          <t xml:space="preserve">134</t>
         </is>
       </c>
       <c r="B20" s="4" t="inlineStr">
@@ -2041,88 +2037,92 @@
       </c>
       <c r="F20" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Bulletin</t>
+          <t xml:space="preserve">Static Bulletin</t>
         </is>
       </c>
       <c r="G20" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">453921</t>
+          <t xml:space="preserve">470717</t>
         </is>
       </c>
       <c r="H20" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">306 I-35 N 0.18 mi N/O 1st St E (Loop 343) WS</t>
-        </is>
-      </c>
-      <c r="I20" s="4"/>
-      <c r="J20" s="4"/>
+          <t xml:space="preserve">10720 I-35 N 0.3 mi S/O Braker Ln E WS</t>
+        </is>
+      </c>
+      <c r="I20" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Austin</t>
+        </is>
+      </c>
+      <c r="J20" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">78753</t>
+        </is>
+      </c>
       <c r="K20" s="10">
-        <v>30.26372</v>
+        <v>30.373336</v>
       </c>
       <c r="L20" s="10">
-        <v>-97.73606</v>
+        <v>-97.679089</v>
       </c>
       <c r="M20" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve">North</t>
         </is>
       </c>
-      <c r="N20" s="4"/>
+      <c r="N20" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Right</t>
+        </is>
+      </c>
       <c r="O20" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">14' x 48'</t>
-        </is>
-      </c>
-      <c r="P20" s="4"/>
-      <c r="Q20" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">I-35 DT HV</t>
-        </is>
-      </c>
+          <t xml:space="preserve">10' x 40'</t>
+        </is>
+      </c>
+      <c r="P20" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Y</t>
+        </is>
+      </c>
+      <c r="Q20" s="4"/>
       <c r="R20" s="6">
-        <v>46209</v>
+        <v>46251</v>
       </c>
       <c r="S20" s="6">
-        <v>46355</v>
+        <v>46383</v>
       </c>
       <c r="T20" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEB - B4670A (Direct).pdf</t>
+          <t xml:space="preserve">Reagan Q3Q4 2026 Bulletin HEB-signed (awaiting RNA President).pdf</t>
         </is>
       </c>
       <c r="U20" s="4">
-        <v>1790665</v>
+        <v>727696</v>
       </c>
       <c r="V20" s="8">
-        <v>20735</v>
+        <v>6350</v>
       </c>
       <c r="W20" s="8"/>
       <c r="X20" s="4"/>
       <c r="Y20" s="4">
-        <v>1.5</v>
+        <v>1.3</v>
       </c>
       <c r="Z20" s="12" t="inlineStr">
         <is>
           <t xml:space="preserve">📐 Spec Sheet</t>
         </is>
       </c>
-      <c r="AA20" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">More Dinner. Less Dinero.</t>
-        </is>
-      </c>
+      <c r="AA20" s="4"/>
       <c r="AB20" s="4"/>
       <c r="AC20" s="6"/>
-      <c r="AD20" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">NCAA</t>
-        </is>
-      </c>
+      <c r="AD20" s="4"/>
     </row>
     <row r="21">
       <c r="A21" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">504</t>
+          <t xml:space="preserve">352</t>
         </is>
       </c>
       <c r="B21" s="5" t="inlineStr">
@@ -2147,92 +2147,88 @@
       </c>
       <c r="F21" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Static Bulletin</t>
+          <t xml:space="preserve">Bulletin</t>
         </is>
       </c>
       <c r="G21" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">453965</t>
+          <t xml:space="preserve">453921</t>
         </is>
       </c>
       <c r="H21" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">11418 RR 2222 250 ft E/O FM 620 N NS</t>
-        </is>
-      </c>
-      <c r="I21" s="5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Austin</t>
-        </is>
-      </c>
-      <c r="J21" s="5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">78730</t>
-        </is>
-      </c>
+          <t xml:space="preserve">306 I-35 N 0.18 mi N/O 1st St E (Loop 343) WS</t>
+        </is>
+      </c>
+      <c r="I21" s="5"/>
+      <c r="J21" s="5"/>
       <c r="K21" s="11">
-        <v>30.40338</v>
+        <v>30.26372</v>
       </c>
       <c r="L21" s="11">
-        <v>-97.85314</v>
+        <v>-97.73606</v>
       </c>
       <c r="M21" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">West</t>
-        </is>
-      </c>
-      <c r="N21" s="5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Left</t>
-        </is>
-      </c>
+          <t xml:space="preserve">North</t>
+        </is>
+      </c>
+      <c r="N21" s="5"/>
       <c r="O21" s="5" t="inlineStr">
         <is>
           <t xml:space="preserve">14' x 48'</t>
         </is>
       </c>
-      <c r="P21" s="5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Y</t>
-        </is>
-      </c>
-      <c r="Q21" s="5"/>
+      <c r="P21" s="5"/>
+      <c r="Q21" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">I-35 DT HV</t>
+        </is>
+      </c>
       <c r="R21" s="7">
-        <v>46251</v>
+        <v>46209</v>
       </c>
       <c r="S21" s="7">
-        <v>46313</v>
+        <v>46355</v>
       </c>
       <c r="T21" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Reagan Q3Q4 2026 Bulletin HEB-signed (awaiting RNA President).pdf</t>
+          <t xml:space="preserve">HEB - B4670A (Direct).pdf</t>
         </is>
       </c>
       <c r="U21" s="5">
-        <v>341814</v>
+        <v>1790665</v>
       </c>
       <c r="V21" s="9">
-        <v>5830</v>
+        <v>20735</v>
       </c>
       <c r="W21" s="9"/>
       <c r="X21" s="5"/>
       <c r="Y21" s="5">
-        <v>0.1</v>
+        <v>1.5</v>
       </c>
       <c r="Z21" s="13" t="inlineStr">
         <is>
           <t xml:space="preserve">📐 Spec Sheet</t>
         </is>
       </c>
-      <c r="AA21" s="5"/>
+      <c r="AA21" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">More Dinner. Less Dinero.</t>
+        </is>
+      </c>
       <c r="AB21" s="5"/>
       <c r="AC21" s="7"/>
-      <c r="AD21" s="5"/>
+      <c r="AD21" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">NCAA</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">9041</t>
+          <t xml:space="preserve">504</t>
         </is>
       </c>
       <c r="B22" s="4" t="inlineStr">
@@ -2262,12 +2258,12 @@
       </c>
       <c r="G22" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">454333</t>
+          <t xml:space="preserve">453965</t>
         </is>
       </c>
       <c r="H22" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">12200 Mo-Pac Expy N (Loop 1) 0.5 mi S/O Parmer Ln W (SR 734) WS</t>
+          <t xml:space="preserve">11418 RR 2222 250 ft E/O FM 620 N NS</t>
         </is>
       </c>
       <c r="I22" s="4" t="inlineStr">
@@ -2277,23 +2273,23 @@
       </c>
       <c r="J22" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">78758</t>
+          <t xml:space="preserve">78730</t>
         </is>
       </c>
       <c r="K22" s="10">
-        <v>30.41426</v>
+        <v>30.40338</v>
       </c>
       <c r="L22" s="10">
-        <v>-97.70797</v>
+        <v>-97.85314</v>
       </c>
       <c r="M22" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">North</t>
+          <t xml:space="preserve">West</t>
         </is>
       </c>
       <c r="N22" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Right</t>
+          <t xml:space="preserve">Left</t>
         </is>
       </c>
       <c r="O22" s="4" t="inlineStr">
@@ -2308,10 +2304,10 @@
       </c>
       <c r="Q22" s="4"/>
       <c r="R22" s="6">
-        <v>46293</v>
+        <v>46251</v>
       </c>
       <c r="S22" s="6">
-        <v>46327</v>
+        <v>46313</v>
       </c>
       <c r="T22" s="4" t="inlineStr">
         <is>
@@ -2319,15 +2315,15 @@
         </is>
       </c>
       <c r="U22" s="4">
-        <v>628643</v>
+        <v>341814</v>
       </c>
       <c r="V22" s="8">
-        <v>20350</v>
+        <v>5830</v>
       </c>
       <c r="W22" s="8"/>
       <c r="X22" s="4"/>
       <c r="Y22" s="4">
-        <v>0.3</v>
+        <v>0.1</v>
       </c>
       <c r="Z22" s="12" t="inlineStr">
         <is>
@@ -2342,7 +2338,7 @@
     <row r="23">
       <c r="A23" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">9073</t>
+          <t xml:space="preserve">9041</t>
         </is>
       </c>
       <c r="B23" s="5" t="inlineStr">
@@ -2372,12 +2368,12 @@
       </c>
       <c r="G23" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">454293</t>
+          <t xml:space="preserve">454333</t>
         </is>
       </c>
       <c r="H23" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">8304 US 290 E 0.3 mi W/O Springdale Rd NS</t>
+          <t xml:space="preserve">12200 Mo-Pac Expy N (Loop 1) 0.5 mi S/O Parmer Ln W (SR 734) WS</t>
         </is>
       </c>
       <c r="I23" s="5" t="inlineStr">
@@ -2387,18 +2383,18 @@
       </c>
       <c r="J23" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">78754</t>
+          <t xml:space="preserve">78758</t>
         </is>
       </c>
       <c r="K23" s="11">
-        <v>30.32867</v>
+        <v>30.41426</v>
       </c>
       <c r="L23" s="11">
-        <v>-97.66214</v>
+        <v>-97.70797</v>
       </c>
       <c r="M23" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">East</t>
+          <t xml:space="preserve">North</t>
         </is>
       </c>
       <c r="N23" s="5" t="inlineStr">
@@ -2418,7 +2414,7 @@
       </c>
       <c r="Q23" s="5"/>
       <c r="R23" s="7">
-        <v>46279</v>
+        <v>46293</v>
       </c>
       <c r="S23" s="7">
         <v>46327</v>
@@ -2429,15 +2425,15 @@
         </is>
       </c>
       <c r="U23" s="5">
-        <v>339031</v>
+        <v>628643</v>
       </c>
       <c r="V23" s="9">
-        <v>3860</v>
+        <v>20350</v>
       </c>
       <c r="W23" s="9"/>
       <c r="X23" s="5"/>
       <c r="Y23" s="5">
-        <v>1.9</v>
+        <v>0.3</v>
       </c>
       <c r="Z23" s="13" t="inlineStr">
         <is>
@@ -2452,7 +2448,7 @@
     <row r="24">
       <c r="A24" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">9078</t>
+          <t xml:space="preserve">9073</t>
         </is>
       </c>
       <c r="B24" s="4" t="inlineStr">
@@ -2482,12 +2478,12 @@
       </c>
       <c r="G24" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">454358</t>
+          <t xml:space="preserve">454293</t>
         </is>
       </c>
       <c r="H24" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">RR 2222 500 ft E/O RR 620 SS</t>
+          <t xml:space="preserve">8304 US 290 E 0.3 mi W/O Springdale Rd NS</t>
         </is>
       </c>
       <c r="I24" s="4" t="inlineStr">
@@ -2497,14 +2493,14 @@
       </c>
       <c r="J24" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">78730</t>
+          <t xml:space="preserve">78754</t>
         </is>
       </c>
       <c r="K24" s="10">
-        <v>30.40252</v>
+        <v>30.32867</v>
       </c>
       <c r="L24" s="10">
-        <v>-97.85297</v>
+        <v>-97.66214</v>
       </c>
       <c r="M24" s="4" t="inlineStr">
         <is>
@@ -2513,7 +2509,7 @@
       </c>
       <c r="N24" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Left</t>
+          <t xml:space="preserve">Right</t>
         </is>
       </c>
       <c r="O24" s="4" t="inlineStr">
@@ -2528,7 +2524,7 @@
       </c>
       <c r="Q24" s="4"/>
       <c r="R24" s="6">
-        <v>46251</v>
+        <v>46279</v>
       </c>
       <c r="S24" s="6">
         <v>46327</v>
@@ -2539,15 +2535,15 @@
         </is>
       </c>
       <c r="U24" s="4">
-        <v>125286</v>
+        <v>339031</v>
       </c>
       <c r="V24" s="8">
-        <v>3750</v>
+        <v>3860</v>
       </c>
       <c r="W24" s="8"/>
       <c r="X24" s="4"/>
       <c r="Y24" s="4">
-        <v>0.1</v>
+        <v>1.9</v>
       </c>
       <c r="Z24" s="12" t="inlineStr">
         <is>
@@ -2562,7 +2558,7 @@
     <row r="25">
       <c r="A25" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">9345</t>
+          <t xml:space="preserve">9078</t>
         </is>
       </c>
       <c r="B25" s="5" t="inlineStr">
@@ -2592,12 +2588,12 @@
       </c>
       <c r="G25" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">14910666</t>
+          <t xml:space="preserve">454358</t>
         </is>
       </c>
       <c r="H25" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">10611 Research Blvd (US 183) 0.2 mi S/O Braker Ln W ES</t>
+          <t xml:space="preserve">RR 2222 500 ft E/O RR 620 SS</t>
         </is>
       </c>
       <c r="I25" s="5" t="inlineStr">
@@ -2607,23 +2603,23 @@
       </c>
       <c r="J25" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">78759</t>
+          <t xml:space="preserve">78730</t>
         </is>
       </c>
       <c r="K25" s="11">
-        <v>30.39775</v>
+        <v>30.40252</v>
       </c>
       <c r="L25" s="11">
-        <v>-97.74553</v>
+        <v>-97.85297</v>
       </c>
       <c r="M25" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">South</t>
+          <t xml:space="preserve">East</t>
         </is>
       </c>
       <c r="N25" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Right</t>
+          <t xml:space="preserve">Left</t>
         </is>
       </c>
       <c r="O25" s="5" t="inlineStr">
@@ -2649,10 +2645,10 @@
         </is>
       </c>
       <c r="U25" s="5">
-        <v>722818</v>
+        <v>125286</v>
       </c>
       <c r="V25" s="9">
-        <v>12925</v>
+        <v>3750</v>
       </c>
       <c r="W25" s="9"/>
       <c r="X25" s="5"/>
@@ -2672,7 +2668,7 @@
     <row r="26">
       <c r="A26" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">9507</t>
+          <t xml:space="preserve">9345</t>
         </is>
       </c>
       <c r="B26" s="4" t="inlineStr">
@@ -2702,12 +2698,12 @@
       </c>
       <c r="G26" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">30640678</t>
+          <t xml:space="preserve">14910666</t>
         </is>
       </c>
       <c r="H26" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">6428 I-35 S 500 ft N/O William Cannon WS</t>
+          <t xml:space="preserve">10611 Research Blvd (US 183) 0.2 mi S/O Braker Ln W ES</t>
         </is>
       </c>
       <c r="I26" s="4" t="inlineStr">
@@ -2717,18 +2713,18 @@
       </c>
       <c r="J26" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">78745</t>
+          <t xml:space="preserve">78759</t>
         </is>
       </c>
       <c r="K26" s="10">
-        <v>30.19184</v>
+        <v>30.39775</v>
       </c>
       <c r="L26" s="10">
-        <v>-97.77013</v>
+        <v>-97.74553</v>
       </c>
       <c r="M26" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">North</t>
+          <t xml:space="preserve">South</t>
         </is>
       </c>
       <c r="N26" s="4" t="inlineStr">
@@ -2748,10 +2744,10 @@
       </c>
       <c r="Q26" s="4"/>
       <c r="R26" s="6">
-        <v>46293</v>
+        <v>46251</v>
       </c>
       <c r="S26" s="6">
-        <v>46376</v>
+        <v>46327</v>
       </c>
       <c r="T26" s="4" t="inlineStr">
         <is>
@@ -2759,10 +2755,10 @@
         </is>
       </c>
       <c r="U26" s="4">
-        <v>870619</v>
+        <v>722818</v>
       </c>
       <c r="V26" s="8">
-        <v>9295</v>
+        <v>12925</v>
       </c>
       <c r="W26" s="8"/>
       <c r="X26" s="4"/>
@@ -2782,7 +2778,7 @@
     <row r="27">
       <c r="A27" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">9672</t>
+          <t xml:space="preserve">9507</t>
         </is>
       </c>
       <c r="B27" s="5" t="inlineStr">
@@ -2812,12 +2808,12 @@
       </c>
       <c r="G27" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">50753247</t>
+          <t xml:space="preserve">30640678</t>
         </is>
       </c>
       <c r="H27" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Hwy 290 W 1370 ft W/O West Gate Blvd NS</t>
+          <t xml:space="preserve">6428 I-35 S 500 ft N/O William Cannon WS</t>
         </is>
       </c>
       <c r="I27" s="5" t="inlineStr">
@@ -2827,18 +2823,18 @@
       </c>
       <c r="J27" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">78735</t>
+          <t xml:space="preserve">78745</t>
         </is>
       </c>
       <c r="K27" s="11">
-        <v>30.232528</v>
+        <v>30.19184</v>
       </c>
       <c r="L27" s="11">
-        <v>-97.805155</v>
+        <v>-97.77013</v>
       </c>
       <c r="M27" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">East</t>
+          <t xml:space="preserve">North</t>
         </is>
       </c>
       <c r="N27" s="5" t="inlineStr">
@@ -2858,10 +2854,10 @@
       </c>
       <c r="Q27" s="5"/>
       <c r="R27" s="7">
-        <v>46251</v>
+        <v>46293</v>
       </c>
       <c r="S27" s="7">
-        <v>46327</v>
+        <v>46376</v>
       </c>
       <c r="T27" s="5" t="inlineStr">
         <is>
@@ -2869,15 +2865,15 @@
         </is>
       </c>
       <c r="U27" s="5">
-        <v>495015</v>
+        <v>870619</v>
       </c>
       <c r="V27" s="9">
-        <v>8450</v>
+        <v>9295</v>
       </c>
       <c r="W27" s="9"/>
       <c r="X27" s="5"/>
       <c r="Y27" s="5">
-        <v>1.9</v>
+        <v>0.1</v>
       </c>
       <c r="Z27" s="13" t="inlineStr">
         <is>
@@ -2892,18 +2888,22 @@
     <row r="28">
       <c r="A28" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">189-3</t>
+          <t xml:space="preserve">9672</t>
         </is>
       </c>
       <c r="B28" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">The Reiss Group</t>
-        </is>
-      </c>
-      <c r="C28" s="4"/>
+          <t xml:space="preserve">Reagan Outdoor</t>
+        </is>
+      </c>
+      <c r="C28" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Karen Goumakos</t>
+        </is>
+      </c>
       <c r="D28" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Lisa@thereissgroup.net</t>
+          <t xml:space="preserve">kgoumakos@reaganusa.com</t>
         </is>
       </c>
       <c r="E28" s="4" t="inlineStr">
@@ -2913,95 +2913,103 @@
       </c>
       <c r="F28" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Bulletin</t>
-        </is>
-      </c>
-      <c r="G28" s="4"/>
+          <t xml:space="preserve">Static Bulletin</t>
+        </is>
+      </c>
+      <c r="G28" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">50753247</t>
+        </is>
+      </c>
       <c r="H28" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">I-35 near Hwy 123 (MP 203.7), 408 Patricia Dr, San Marcos, TX</t>
-        </is>
-      </c>
-      <c r="I28" s="4"/>
-      <c r="J28" s="4"/>
+          <t xml:space="preserve">Hwy 290 W 1370 ft W/O West Gate Blvd NS</t>
+        </is>
+      </c>
+      <c r="I28" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Austin</t>
+        </is>
+      </c>
+      <c r="J28" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">78735</t>
+        </is>
+      </c>
       <c r="K28" s="10">
-        <v>29.86349</v>
+        <v>30.232528</v>
       </c>
       <c r="L28" s="10">
-        <v>-97.94506</v>
-      </c>
-      <c r="M28" s="4"/>
-      <c r="N28" s="4"/>
+        <v>-97.805155</v>
+      </c>
+      <c r="M28" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">East</t>
+        </is>
+      </c>
+      <c r="N28" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Right</t>
+        </is>
+      </c>
       <c r="O28" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">12'' x 40''</t>
-        </is>
-      </c>
-      <c r="P28" s="4"/>
-      <c r="Q28" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">SM3 GO</t>
-        </is>
-      </c>
+          <t xml:space="preserve">14' x 48'</t>
+        </is>
+      </c>
+      <c r="P28" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Y</t>
+        </is>
+      </c>
+      <c r="Q28" s="4"/>
       <c r="R28" s="6">
-        <v>46237</v>
+        <v>46251</v>
       </c>
       <c r="S28" s="6">
-        <v>46355</v>
+        <v>46327</v>
       </c>
       <c r="T28" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Sam Marcos_GD.pdf</t>
+          <t xml:space="preserve">Reagan Q3Q4 2026 Bulletin HEB-signed (awaiting RNA President).pdf</t>
         </is>
       </c>
       <c r="U28" s="4">
-        <v>367525</v>
+        <v>495015</v>
       </c>
       <c r="V28" s="8">
-        <v>3090</v>
+        <v>8450</v>
       </c>
       <c r="W28" s="8"/>
       <c r="X28" s="4"/>
       <c r="Y28" s="4">
-        <v>0.9</v>
+        <v>1.9</v>
       </c>
       <c r="Z28" s="12" t="inlineStr">
         <is>
           <t xml:space="preserve">📐 Spec Sheet</t>
         </is>
       </c>
-      <c r="AA28" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">GO: Coming Soon</t>
-        </is>
-      </c>
+      <c r="AA28" s="4"/>
       <c r="AB28" s="4"/>
       <c r="AC28" s="6"/>
-      <c r="AD28" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">GO: Date Reveal</t>
-        </is>
-      </c>
+      <c r="AD28" s="4"/>
     </row>
     <row r="29">
       <c r="A29" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">203-8051L</t>
+          <t xml:space="preserve">189-3</t>
         </is>
       </c>
       <c r="B29" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Theon Properties</t>
-        </is>
-      </c>
-      <c r="C29" s="5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Mike Elliott (Elliott Properties Inc)</t>
-        </is>
-      </c>
+          <t xml:space="preserve">The Reiss Group</t>
+        </is>
+      </c>
+      <c r="C29" s="5"/>
       <c r="D29" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">mike@elliottpropertiesinc.com</t>
+          <t xml:space="preserve">Lisa@thereissgroup.net</t>
         </is>
       </c>
       <c r="E29" s="5" t="inlineStr">
@@ -3017,77 +3025,175 @@
       <c r="G29" s="5"/>
       <c r="H29" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">IH-35 NB, 0.5 mi south of Ronald Reagan Blvd — SW corner IH-35 &amp; Ronald Reagan ("Sign No. 2"), 8360 I-35 frontage, Georgetown/Jarrell line</t>
-        </is>
-      </c>
-      <c r="I29" s="5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Jarrell</t>
-        </is>
-      </c>
-      <c r="J29" s="5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">78626</t>
-        </is>
-      </c>
+          <t xml:space="preserve">I-35 near Hwy 123 (MP 203.7), 408 Patricia Dr, San Marcos, TX</t>
+        </is>
+      </c>
+      <c r="I29" s="5"/>
+      <c r="J29" s="5"/>
       <c r="K29" s="11">
-        <v>30.7645</v>
+        <v>29.86349</v>
       </c>
       <c r="L29" s="11">
-        <v>-97.6302</v>
-      </c>
-      <c r="M29" s="5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">South</t>
-        </is>
-      </c>
-      <c r="N29" s="5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Left</t>
-        </is>
-      </c>
+        <v>-97.94506</v>
+      </c>
+      <c r="M29" s="5"/>
+      <c r="N29" s="5"/>
       <c r="O29" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">14x48</t>
-        </is>
-      </c>
-      <c r="P29" s="5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Y</t>
-        </is>
-      </c>
-      <c r="Q29" s="5"/>
+          <t xml:space="preserve">12'' x 40''</t>
+        </is>
+      </c>
+      <c r="P29" s="5"/>
+      <c r="Q29" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">SM3 GO</t>
+        </is>
+      </c>
       <c r="R29" s="7">
-        <v>46296</v>
+        <v>46237</v>
       </c>
       <c r="S29" s="7">
-        <v>47026</v>
+        <v>46355</v>
       </c>
       <c r="T29" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Theon 8051L lease EXECUTED 8-4-26 (both signed).pdf</t>
+          <t xml:space="preserve">Sam Marcos_GD.pdf</t>
         </is>
       </c>
       <c r="U29" s="5">
-        <v>256803</v>
+        <v>367525</v>
       </c>
       <c r="V29" s="9">
-        <v>1000</v>
+        <v>3090</v>
       </c>
       <c r="W29" s="9"/>
       <c r="X29" s="5"/>
       <c r="Y29" s="5">
-        <v>8.4</v>
+        <v>0.9</v>
       </c>
       <c r="Z29" s="13" t="inlineStr">
         <is>
           <t xml:space="preserve">📐 Spec Sheet</t>
         </is>
       </c>
-      <c r="AA29" s="5"/>
+      <c r="AA29" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">GO: Coming Soon</t>
+        </is>
+      </c>
       <c r="AB29" s="5"/>
       <c r="AC29" s="7"/>
-      <c r="AD29" s="5"/>
+      <c r="AD29" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">GO: Date Reveal</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">203-8051L</t>
+        </is>
+      </c>
+      <c r="B30" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Theon Properties</t>
+        </is>
+      </c>
+      <c r="C30" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Mike Elliott (Elliott Properties Inc)</t>
+        </is>
+      </c>
+      <c r="D30" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">mike@elliottpropertiesinc.com</t>
+        </is>
+      </c>
+      <c r="E30" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Central</t>
+        </is>
+      </c>
+      <c r="F30" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Bulletin</t>
+        </is>
+      </c>
+      <c r="G30" s="4"/>
+      <c r="H30" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">IH-35 NB, 0.5 mi south of Ronald Reagan Blvd — SW corner IH-35 &amp; Ronald Reagan ("Sign No. 2"), 8360 I-35 frontage, Georgetown/Jarrell line</t>
+        </is>
+      </c>
+      <c r="I30" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Jarrell</t>
+        </is>
+      </c>
+      <c r="J30" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">78626</t>
+        </is>
+      </c>
+      <c r="K30" s="10">
+        <v>30.7645</v>
+      </c>
+      <c r="L30" s="10">
+        <v>-97.6302</v>
+      </c>
+      <c r="M30" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">South</t>
+        </is>
+      </c>
+      <c r="N30" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Left</t>
+        </is>
+      </c>
+      <c r="O30" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">14x48</t>
+        </is>
+      </c>
+      <c r="P30" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Y</t>
+        </is>
+      </c>
+      <c r="Q30" s="4"/>
+      <c r="R30" s="6">
+        <v>46296</v>
+      </c>
+      <c r="S30" s="6">
+        <v>47026</v>
+      </c>
+      <c r="T30" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Theon 8051L lease EXECUTED 8-4-26 (both signed).pdf</t>
+        </is>
+      </c>
+      <c r="U30" s="4">
+        <v>256803</v>
+      </c>
+      <c r="V30" s="8">
+        <v>1000</v>
+      </c>
+      <c r="W30" s="8"/>
+      <c r="X30" s="4"/>
+      <c r="Y30" s="4">
+        <v>8.4</v>
+      </c>
+      <c r="Z30" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">📐 Spec Sheet</t>
+        </is>
+      </c>
+      <c r="AA30" s="4"/>
+      <c r="AB30" s="4"/>
+      <c r="AC30" s="6"/>
+      <c r="AD30" s="4"/>
     </row>
   </sheetData>
   <autoFilter ref="A3:AD3"/>
@@ -3120,6 +3226,7 @@
     <hyperlink ref="Z27" r:id="rIdH22"/>
     <hyperlink ref="Z28" r:id="rIdH23"/>
     <hyperlink ref="Z29" r:id="rIdH24"/>
+    <hyperlink ref="Z30" r:id="rIdH25"/>
   </hyperlinks>
 </worksheet>
 </file>
--- a/region/Central-overview-grid.xlsx
+++ b/region/Central-overview-grid.xlsx
@@ -150,7 +150,7 @@
     <row r="1" ht="20" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">H-E-B  |  Region Overview information — Central — generated 8/11/2026</t>
+          <t xml:space="preserve">H-E-B  |  Region Overview information — Central — generated 8/18/2026</t>
         </is>
       </c>
     </row>
@@ -1857,7 +1857,7 @@
       </c>
       <c r="N18" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Left</t>
+          <t xml:space="preserve">Right</t>
         </is>
       </c>
       <c r="O18" s="4" t="inlineStr">
